--- a/marketing/NineTilesPuzzle_ContentCalendar.xlsx
+++ b/marketing/NineTilesPuzzle_ContentCalendar.xlsx
@@ -10,9 +10,11 @@
   <sheets>
     <sheet name="Calendar" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Video Shot Lists" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Calendar!$A$1:$H$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Video Shot Lists'!$A$1:$H$18</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="248">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -426,6 +428,348 @@
   </si>
   <si>
     <t xml:space="preserve">YT Shorts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to record (shot list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-screen text &amp; timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music vibe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editing notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caption (copy-paste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfying Reveal #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-15s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick a vivid, high-contrast photo ahead of time (via the Photos-library source, not a random fetch, so it reads well small). Screen-record: 1s on the intact photo, the shuffle into a 4x4/5x5 grid, then a smooth practiced solve. Take 2-3 tries, keep the cleanest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None for first 8s - let the visual carry it. Last 2s: 'Free beta - link in bio, keep it forever' in accent orange (#FF8A3D).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upbeat trending 'satisfying' audio - check TikTok Trending Sounds the day you post.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed up the shuffle 2x. Real time (or a hair of slow-mo) on the final few moves of the solve so the 'aha' lands. Hard cut, hold 1s on the completed image before the CTA card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watch this come back together. Free beta open now - keep the full app forever if you test it. Link in bio. #satisfying #puzzle #iosgames #mobilegame #indiedev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode Spotlight: Slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-20s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Slide mode. Solve a few tiles normally, then deliberately nudge an already-placed tile to show the twist, finish the solve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-1s title card 'SLIDE MODE'. Caption timed to the nudge: 'tiles you've placed... can still move'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean, mid-energy beat - start of a consistent 'mode spotlight' music family.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briefly slow down right as you nudge the placed tile so it reads clearly; real time otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode 1 of 7: Slide. Even the tiles you've already placed aren't totally safe. Free beta - link in bio. #iosgames #puzzlegame #indiedev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Forever Hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-12s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast montage - reuse 2-3 clips from the first satisfying reveal as backdrop. No new gameplay needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text-driven: 'Beta testers keep the FULL APP' -&gt; 'FREE. FOREVER.' -&gt; 'Link in bio'. Text is the star, gameplay is backdrop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upbeat, with text timed to hit on the beat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut on the beat; keep each text card on screen ~1s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The best time to try 9 Tiles Puzzle is before it launches. Beta testers keep the full app free, forever. Link in bio. #iosdev #indiedev #freeapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode Spotlight: Swap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Swap mode. Show swapping two tiles, then a correct tile locking permanently the moment it lands right.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title card 'SWAP MODE'. Caption: 'swap any two tiles' then 'get it right and it locks - for good'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same clean mid-energy family as Slide, for series consistency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick zoom/flash the instant a tile locks in place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode 2 of 7: Swap - land a tile correctly and it's locked in for good. Free beta, link in bio. #puzzlegame #iosgames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfying Reveal #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same format as Reveal #1, different photo genre for variety (e.g. a pet or food photo - different color palette).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as Reveal #1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A different trending track than Reveal #1 - don't repeat audio back to back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat the proven structure from Reveal #1 exactly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round two. Free beta - link in bio, keep it forever. #satisfying #puzzle #mobilegame #indiedev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind the Scenes: Building It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-25s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen-record a short Xcode session - real SwiftUI code, running the simulator. Optional: a couple seconds of you on camera if comfortable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Building this solo.' then one concrete detail, e.g. 'Swift 6, SwiftUI, no third-party UI libraries.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calmer, lo-fi/coding-vibe track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed-ramp the typing/scrolling 3-4x; real time on the simulator running the feature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo dev diary: building 9 Tiles Puzzle in SwiftUI. Beta's open if you want to help test - link in bio. #buildinpublic #indiedev #SwiftUI #iosdev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode Spotlight: Time Trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the countdown timer under pressure, then cut to the Gauntlet Ladder screen (the 10-stage climb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'TIME TRIAL' then 'Gauntlet Ladder: 10 stages'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher-energy, tense track matching the time pressure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slight speed-up on the clock ticking to build tension; real time on the actual solve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode 3 of 7: Time Trial. Beat the clock, then climb all 10 stages of the Gauntlet Ladder. Free beta, link in bio. #iosgames #puzzlegame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Daily Challenge, solve the day's puzzle, then show the calendar view with the streak marked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'One puzzle. Every day.' then 'track your streak'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm, steady mid-tempo track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real time throughout; brief pause/zoom on the calendar streak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One seeded puzzle a day, and a calendar to track (or replay) your streak. Free beta, link in bio. #dailychallenge #iosgames #puzzlegame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Mode Reveal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start the mode, capture the moment the photo turns out recolored/mirrored/flipped from what you expected, then the solve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimal - just a 'CHAOS MODE' title card, then nothing until the CTA. Let the twist speak for itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A track with a hard 'drop' timed to the recolor/mirror reveal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard cut or glitch-style transition right at the reveal for maximum surprise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode 7 of 7: Chaos. You don't even know what the photo looks like until it's too late. Free beta, link in bio. #puzzlegame #iosgames #satisfying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode Spotlight: Haze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show tiles obscured by drifting fog, physically shake the phone on camera to reveal briefly, keep solving mostly blind.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'HAZE MODE' then 'shake to peek'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moody/ambient into a beat drop right as you shake.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick zoom/flash on the shake moment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode 4 of 7: Haze. The tiles hide behind fog - shake your phone to peek. Free beta, link in bio. #iosgames #puzzlegame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achievements &amp; Wall of Fame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture an achievement unlocking (toast/animation), then pan the Wall of Fame cork board of pinned record cards - flick one to show its swing physics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'39 achievements' then 'Wall of Fame - your best records, pinned'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celebratory, rewarding track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow-mo on the achievement unlock animation; real time flicking a Wall of Fame card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 achievements to unlock, plus a Wall of Fame for your best records - physics and all. Free beta, link in bio. #iosgames #achievements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widgets + Live Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record from the Lock Screen showing the Live Activity / Dynamic Island tracking an in-progress puzzle, then swipe home and show the 3 widgets (Daily Challenge, Streaks &amp; Records, Resume Game).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Track your puzzle from the Lock Screen' then '3 home screen widgets'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean, modern tech-demo style track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real time; end on tapping a widget to deep-link back into the game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your puzzle, tracked from the Lock Screen and Dynamic Island - plus 3 home screen widgets. Free beta, link in bio. #iosgames #widgets #iOS26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Countdown / Preorder Reminder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick highlight montage reusing your best clips so far - no new filming required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'9 days.' then '9 Tiles Puzzle' then 'Preorder now - link in bio'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building, anticipatory track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut on the beat; text-forward, gameplay as backdrop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 days until launch. Preorder now, link in bio. #iosgames #launchday #indiedev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed-Solve Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record a genuinely fast, clean solve with the in-game timer visible on screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'My time: [X.XX]s' then 'beat it?' as a duet/stitch prompt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-energy track suited to a challenge format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep it real-time so the time is legitimate; optional slow-mo replay of just the final move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My best time - think you can beat it? Duet this with your run. Free beta, link in bio. #speedrun #puzzlegame #challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta Tester Highlight Reel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-30s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compile 3-5 short clips or quotes from real beta testers (get their OK first) - their gameplay, or text-over-video of what they told you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each tester's quote as its own caption card; first names only unless they're happy to be tagged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm, community-feel track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick cuts between testers, ~3-5s each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What beta testers are saying. Launching Monday - link in bio. #buildinpublic #indiedev #betatest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Launch Day Announcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-cut your best existing solve clip, or freshly record downloading/opening the app live from the App Store.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'IT'S LIVE' then 'Download now - link in bio'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celebratory, high-energy trending track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast cuts; confetti/celebration-style text animation if your editor has one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Tiles Puzzle is live on the App Store. Download now, link in bio. #launchday #iosgames #newapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Launch Thank You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A calmer, more personal clip - optionally you on camera, or text over a montage of the campaign's best moments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Thank you.' then 'If you're enjoying it, a review means everything' then the App Store link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm, low-key track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slower pacing than launch day; montage of highlights from the whole campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you to everyone who tested, shared, and downloaded. If you're enjoying 9 Tiles Puzzle, a review would mean a lot. Link in bio. #indiedev #iosgames #thankyou</t>
   </si>
 </sst>
 </file>
@@ -518,7 +862,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -565,6 +909,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAEAEA"/>
         <bgColor rgb="FFE4E1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8A3D"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7FB"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -617,7 +973,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -698,6 +1054,26 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +1083,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -780,6 +1156,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF7F7FB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF8A3D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -818,7 +1217,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEAEAEA"/>
       <rgbColor rgb="FFDFF5E3"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFF7F7FB"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -827,7 +1226,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8A3D"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF969696"/>
@@ -845,6 +1244,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -2681,4 +3084,503 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H18"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>